--- a/web_design_forms/005_web_developer_programmer_application_form--web_design_forms.xlsx
+++ b/web_design_forms/005_web_developer_programmer_application_form--web_design_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'programming_languages',_'label':_'programming_languages',_'type':_'select_one',_'options':_[{'id':_9,_'name':_'javascript'},_{'id':_10,_'name':_'html'},_{'id':_11,_'name':_'css'},_{'id':_12,_'name':_'python'},_{'id':_13,_'name':_'c++'}]}</t>
+          <t>programming_languages</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'programming_languages', 'label': 'Programming Languages', 'type': 'select_one', 'options': [{'id': 9, 'name': 'JavaScript'}, {'id': 10, 'name': 'HTML'}, {'id': 11, 'name': 'CSS'}, {'id': 12, 'name': 'Python'}, {'id': 13, 'name': 'C++'}]}</t>
+          <t>Programming Languages</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'frameworks',_'label':_'frameworks',_'type':_'select_multiple',_'options':_[{'id':_15,_'name':_'react'},_{'id':_16,_'name':_'angular'},_{'id':_17,_'name':_'vue'}]}</t>
+          <t>frameworks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'frameworks', 'label': 'Frameworks', 'type': 'select_multiple', 'options': [{'id': 15, 'name': 'React'}, {'id': 16, 'name': 'Angular'}, {'id': 17, 'name': 'Vue'}]}</t>
+          <t>Frameworks</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'databases',_'label':_'databases',_'type':_'select_multiple',_'options':_[{'id':_19,_'name':_'mongodb'},_{'id':_20,_'name':_'mysql'},_{'id':_21,_'name':_'postgresql'}]}</t>
+          <t>databases</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'databases', 'label': 'Databases', 'type': 'select_multiple', 'options': [{'id': 19, 'name': 'MongoDB'}, {'id': 20, 'name': 'MySQL'}, {'id': 21, 'name': 'PostgreSQL'}]}</t>
+          <t>Databases</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'certifications',_'label':_'certifications',_'type':_'select_multiple',_'options':_[{'id':_23,_'name':_'comptia'},_{'id':_24,_'name':_'aws'},_{'id':_25,_'name':_'google_cloud'}]}</t>
+          <t>certifications</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'certifications', 'label': 'Certifications', 'type': 'select_multiple', 'options': [{'id': 23, 'name': 'CompTIA'}, {'id': 24, 'name': 'AWS'}, {'id': 25, 'name': 'Google Cloud'}]}</t>
+          <t>Certifications</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_27,_'name':_'project1',_'label':_'project_1',_'type':_'select_one',_'options':_[{'id':_28,_'name':_'project_1'},_{'id':_29,_'name':_'project_2'},_{'id':_30,_'name':_'project_3'},_{'id':_31,_'name':_'project_4'}]}</t>
+          <t>project_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 27, 'name': 'project1', 'label': 'Project 1', 'type': 'select_one', 'options': [{'id': 28, 'name': 'Project 1'}, {'id': 29, 'name': 'Project 2'}, {'id': 30, 'name': 'Project 3'}, {'id': 31, 'name': 'Project 4'}]}</t>
+          <t>Project 1</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'app',_'label':_'apps',_'type':_'select_multiple',_'options':_[{'id':_33,_'name':_'app1'},_{'id':_34,_'name':_'app2'},_{'id':_35,_'name':_'app3'}]}</t>
+          <t>apps</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'app', 'label': 'Apps', 'type': 'select_multiple', 'options': [{'id': 33, 'name': 'app1'}, {'id': 34, 'name': 'app2'}, {'id': 35, 'name': 'app3'}]}</t>
+          <t>Apps</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_36,_'name':_'website',_'label':_'website',_'type':_'select_multiple',_'options':_[{'id':_37,_'name':_'website1'},_{'id':_38,_'name':_'website2'},_{'id':_39,_'name':_'website3'}]}</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 36, 'name': 'website', 'label': 'Website', 'type': 'select_multiple', 'options': [{'id': 37, 'name': 'website1'}, {'id': 38, 'name': 'website2'}, {'id': 39, 'name': 'website3'}]}</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_'github',_'label':_'github_profile',_'type':_'text',_'options':_[]}</t>
+          <t>github_profile</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 'github', 'label': 'Github Profile', 'type': 'text', 'options': []}</t>
+          <t>Github Profile</t>
         </is>
       </c>
     </row>
